--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260618.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260618.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ETN US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>伊頓公開有限公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>87,630</t>
+          <t>35,853</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.02%</t>
+          <t>10.92%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ETN US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>伊頓公開有限公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>36,253</t>
+          <t>86,630</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.99%</t>
+          <t>10.03%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>101,079</t>
+          <t>99,979</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.49%</t>
+          <t>9.14%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>39,788</t>
+          <t>39,388</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>8.03%</t>
+          <t>7.59%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>218,390</t>
+          <t>215,990</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.28%</t>
+          <t>5.14%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>54,828</t>
+          <t>54,228</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.90%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>116,148</t>
+          <t>114,848</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>3.90%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>125,968</t>
+          <t>124,568</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>65,978</t>
+          <t>65,278</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>21,686</t>
+          <t>21,486</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>131,022</t>
+          <t>129,522</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
@@ -853,56 +853,56 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>60,683</t>
+          <t>59,983</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>Exelon Corp</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>27,197</t>
+          <t>150,828</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Exelon Corp</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>152,528</t>
+          <t>26,897</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>25,214</t>
+          <t>24,914</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>69,720</t>
+          <t>68,920</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12,687</t>
+          <t>12,587</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>55,658</t>
+          <t>55,058</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1007,210 +1007,210 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>41,158</t>
+          <t>40,658</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>36,381</t>
+          <t>56,706</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>57,306</t>
+          <t>24,608</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>86,169</t>
+          <t>35,981</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>24,908</t>
+          <t>5,407</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>56,020</t>
+          <t>85,169</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>34,069</t>
+          <t>55,420</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>5,507</t>
+          <t>33,669</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>52,626</t>
+          <t>9,976</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>10,076</t>
+          <t>52,026</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1227,78 +1227,78 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>23,174</t>
+          <t>22,874</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>30,851</t>
+          <t>14,630</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,830</t>
+          <t>11,814</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>11,914</t>
+          <t>30,551</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>84,012</t>
+          <t>83,112</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>106,381</t>
+          <t>105,181</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>33,923</t>
+          <t>33,523</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>163,321</t>
+          <t>161,521</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1403,78 +1403,78 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>34,345</t>
+          <t>33,945</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7,540</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>7,640</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>28,850</t>
+          <t>6,477</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1491,34 +1491,34 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>48,660</t>
+          <t>48,160</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>6,577</t>
+          <t>28,550</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1535,56 +1535,56 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>15,022</t>
+          <t>14,822</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>18,047</t>
+          <t>4,086</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>4,086</t>
+          <t>17,847</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>105,753</t>
+          <t>104,553</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>26,319</t>
+          <t>26,019</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,976</t>
+          <t>8,876</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>20,649</t>
+          <t>20,449</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>42,816</t>
+          <t>42,316</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>142,616,269</t>
+          <t>140,844,558</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
